--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -72146,7 +72146,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 00:40</t>
+          <t>2026-10-24 06:29</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -72146,7 +72146,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-24 06:29</t>
+          <t>2026-10-24 12:28</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -72230,7 +72230,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 00:30</t>
+          <t>2026-10-25 06:31</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -72230,7 +72230,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 06:31</t>
+          <t>2026-10-25 12:28</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -72230,7 +72230,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 12:28</t>
+          <t>2026-10-25 18:26</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -72230,7 +72230,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 18:26</t>
+          <t>2026-10-26 00:43</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -72230,7 +72230,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-26 00:43</t>
+          <t>2026-10-26 06:40</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$L$1694</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$L$1697</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1694"/>
+  <dimension ref="A1:L1697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27805,7 +27805,7 @@
       </c>
       <c r="K639" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/bermudasalent_5EDITARFOTOS.jpg?v=1792881235</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/bermudasalent_5EDITARFOTOS_5EDITARFOTOS_5EDITARFOTOS.jpg?v=1793023831</t>
         </is>
       </c>
       <c r="L639" s="2" t="n">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="K803" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-06-22at3.07.16PM.jpg?v=1782239978</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/camibusonoadcollage_5EDITARFOTOS_5EDITARFOTOS.jpg?v=1793024280</t>
         </is>
       </c>
       <c r="L803" s="2" t="n">
@@ -68688,11 +68688,11 @@
     </row>
     <row r="1613">
       <c r="A1613" s="2" t="n">
-        <v>15435987812419</v>
+        <v>15440188735555</v>
       </c>
       <c r="B1613" s="2" t="inlineStr">
         <is>
-          <t>outfit polonia old money</t>
+          <t>outfit padre e hijo corsol</t>
         </is>
       </c>
       <c r="C1613" s="2" t="inlineStr">
@@ -68716,12 +68716,12 @@
       <c r="I1613" s="2" t="inlineStr"/>
       <c r="J1613" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-polonia-old-money-2</t>
+          <t>https://tiendasopenmind.com/products/outfit-padre-e-hijo-corsol</t>
         </is>
       </c>
       <c r="K1613" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/e1523dab-fd6a-43ce-9d71-c5eb36c5a4d3.jpg?v=1792772601</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/0c38efcc-1cb1-4207-b6f2-ee90addcde76.jpg?v=1793024425</t>
         </is>
       </c>
       <c r="L1613" s="2" t="n">
@@ -68730,11 +68730,11 @@
     </row>
     <row r="1614">
       <c r="A1614" s="2" t="n">
-        <v>15435987320899</v>
+        <v>15440188047427</v>
       </c>
       <c r="B1614" s="2" t="inlineStr">
         <is>
-          <t>outfit polonia old money</t>
+          <t>outfit padre e hijo nivel</t>
         </is>
       </c>
       <c r="C1614" s="2" t="inlineStr">
@@ -68758,12 +68758,12 @@
       <c r="I1614" s="2" t="inlineStr"/>
       <c r="J1614" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-polonia-old-money-1</t>
+          <t>https://tiendasopenmind.com/products/outfit-padre-e-hijo-nivel</t>
         </is>
       </c>
       <c r="K1614" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/6ce680a6-c1c8-4a7b-8954-d2f8dca7f540.jpg?v=1792772579</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/fe5fa9ca-eba6-4ba7-bbaa-a83b0c8f69f2.jpg?v=1793024319</t>
         </is>
       </c>
       <c r="L1614" s="2" t="n">
@@ -68772,11 +68772,11 @@
     </row>
     <row r="1615">
       <c r="A1615" s="2" t="n">
-        <v>15435986862147</v>
+        <v>15440188702787</v>
       </c>
       <c r="B1615" s="2" t="inlineStr">
         <is>
-          <t>outfit polonia old money</t>
+          <t>outfit padre e hijo rayando</t>
         </is>
       </c>
       <c r="C1615" s="2" t="inlineStr">
@@ -68800,12 +68800,12 @@
       <c r="I1615" s="2" t="inlineStr"/>
       <c r="J1615" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-polonia-old-money</t>
+          <t>https://tiendasopenmind.com/products/outfit-padre-e-hijo-rayando</t>
         </is>
       </c>
       <c r="K1615" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/93ab625d-6d8c-41ab-9122-84bc763d28eb.jpg?v=1792772560</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/60e6e18c-18a1-42f2-a739-837dabb92546.jpg?v=1793024397</t>
         </is>
       </c>
       <c r="L1615" s="2" t="n">
@@ -68814,11 +68814,11 @@
     </row>
     <row r="1616">
       <c r="A1616" s="2" t="n">
-        <v>15435982209091</v>
+        <v>15435987812419</v>
       </c>
       <c r="B1616" s="2" t="inlineStr">
         <is>
-          <t>outfit reimbol OLD MONEY</t>
+          <t>outfit polonia old money</t>
         </is>
       </c>
       <c r="C1616" s="2" t="inlineStr">
@@ -68842,12 +68842,12 @@
       <c r="I1616" s="2" t="inlineStr"/>
       <c r="J1616" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-reimbol-old-money</t>
+          <t>https://tiendasopenmind.com/products/outfit-polonia-old-money-2</t>
         </is>
       </c>
       <c r="K1616" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/aa255f35-8592-40d8-a316-ca84d0148bc7.jpg?v=1792772335</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/e1523dab-fd6a-43ce-9d71-c5eb36c5a4d3.jpg?v=1792772601</t>
         </is>
       </c>
       <c r="L1616" s="2" t="n">
@@ -68856,11 +68856,11 @@
     </row>
     <row r="1617">
       <c r="A1617" s="2" t="n">
-        <v>15435983421507</v>
+        <v>15435987320899</v>
       </c>
       <c r="B1617" s="2" t="inlineStr">
         <is>
-          <t>outfit reimbol old money</t>
+          <t>outfit polonia old money</t>
         </is>
       </c>
       <c r="C1617" s="2" t="inlineStr">
@@ -68884,12 +68884,12 @@
       <c r="I1617" s="2" t="inlineStr"/>
       <c r="J1617" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-reimbol-old-money-2</t>
+          <t>https://tiendasopenmind.com/products/outfit-polonia-old-money-1</t>
         </is>
       </c>
       <c r="K1617" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/eca45647-4bbc-4b77-97d0-d4c9607d01f1.jpg?v=1792772401</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/6ce680a6-c1c8-4a7b-8954-d2f8dca7f540.jpg?v=1792772579</t>
         </is>
       </c>
       <c r="L1617" s="2" t="n">
@@ -68898,11 +68898,11 @@
     </row>
     <row r="1618">
       <c r="A1618" s="2" t="n">
-        <v>15435982962755</v>
+        <v>15435986862147</v>
       </c>
       <c r="B1618" s="2" t="inlineStr">
         <is>
-          <t>outfit reimbol old money</t>
+          <t>outfit polonia old money</t>
         </is>
       </c>
       <c r="C1618" s="2" t="inlineStr">
@@ -68926,12 +68926,12 @@
       <c r="I1618" s="2" t="inlineStr"/>
       <c r="J1618" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-reimbol-old-money-1</t>
+          <t>https://tiendasopenmind.com/products/outfit-polonia-old-money</t>
         </is>
       </c>
       <c r="K1618" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/802c07b8-d5dd-425d-8ce2-ef9e08a64d30.jpg?v=1792772380</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/93ab625d-6d8c-41ab-9122-84bc763d28eb.jpg?v=1792772560</t>
         </is>
       </c>
       <c r="L1618" s="2" t="n">
@@ -68940,11 +68940,11 @@
     </row>
     <row r="1619">
       <c r="A1619" s="2" t="n">
-        <v>15436002164803</v>
+        <v>15435982209091</v>
       </c>
       <c r="B1619" s="2" t="inlineStr">
         <is>
-          <t>outfit sender old money</t>
+          <t>outfit reimbol OLD MONEY</t>
         </is>
       </c>
       <c r="C1619" s="2" t="inlineStr">
@@ -68968,12 +68968,12 @@
       <c r="I1619" s="2" t="inlineStr"/>
       <c r="J1619" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-sender-old-money-3</t>
+          <t>https://tiendasopenmind.com/products/outfit-reimbol-old-money</t>
         </is>
       </c>
       <c r="K1619" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/cb41e6c3-6fc3-4411-99f6-442b248f89c1.jpg?v=1792773237</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/aa255f35-8592-40d8-a316-ca84d0148bc7.jpg?v=1792772335</t>
         </is>
       </c>
       <c r="L1619" s="2" t="n">
@@ -68982,11 +68982,11 @@
     </row>
     <row r="1620">
       <c r="A1620" s="2" t="n">
-        <v>15436001607747</v>
+        <v>15435983421507</v>
       </c>
       <c r="B1620" s="2" t="inlineStr">
         <is>
-          <t>outfit sender old money</t>
+          <t>outfit reimbol old money</t>
         </is>
       </c>
       <c r="C1620" s="2" t="inlineStr">
@@ -69010,12 +69010,12 @@
       <c r="I1620" s="2" t="inlineStr"/>
       <c r="J1620" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-sender-old-money-2</t>
+          <t>https://tiendasopenmind.com/products/outfit-reimbol-old-money-2</t>
         </is>
       </c>
       <c r="K1620" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/804d0344-d2a4-4b97-8bd8-18ecc0ad49c1.jpg?v=1792773209</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/eca45647-4bbc-4b77-97d0-d4c9607d01f1.jpg?v=1792772401</t>
         </is>
       </c>
       <c r="L1620" s="2" t="n">
@@ -69024,11 +69024,11 @@
     </row>
     <row r="1621">
       <c r="A1621" s="2" t="n">
-        <v>15435996692547</v>
+        <v>15435982962755</v>
       </c>
       <c r="B1621" s="2" t="inlineStr">
         <is>
-          <t>outfit sender old money</t>
+          <t>outfit reimbol old money</t>
         </is>
       </c>
       <c r="C1621" s="2" t="inlineStr">
@@ -69052,12 +69052,12 @@
       <c r="I1621" s="2" t="inlineStr"/>
       <c r="J1621" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-sender-old-money-1</t>
+          <t>https://tiendasopenmind.com/products/outfit-reimbol-old-money-1</t>
         </is>
       </c>
       <c r="K1621" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/5abdaa37-247a-4c94-b0de-d2868d8290af.jpg?v=1792772981</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/802c07b8-d5dd-425d-8ce2-ef9e08a64d30.jpg?v=1792772380</t>
         </is>
       </c>
       <c r="L1621" s="2" t="n">
@@ -69066,7 +69066,7 @@
     </row>
     <row r="1622">
       <c r="A1622" s="2" t="n">
-        <v>15435995414595</v>
+        <v>15436002164803</v>
       </c>
       <c r="B1622" s="2" t="inlineStr">
         <is>
@@ -69094,12 +69094,12 @@
       <c r="I1622" s="2" t="inlineStr"/>
       <c r="J1622" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-sender-old-money</t>
+          <t>https://tiendasopenmind.com/products/outfit-sender-old-money-3</t>
         </is>
       </c>
       <c r="K1622" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/98bea179-f1a2-4c98-8055-535a78452666.jpg?v=1792772914</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/cb41e6c3-6fc3-4411-99f6-442b248f89c1.jpg?v=1792773237</t>
         </is>
       </c>
       <c r="L1622" s="2" t="n">
@@ -69108,11 +69108,11 @@
     </row>
     <row r="1623">
       <c r="A1623" s="2" t="n">
-        <v>15435994660931</v>
+        <v>15436001607747</v>
       </c>
       <c r="B1623" s="2" t="inlineStr">
         <is>
-          <t>outfit silvio old money</t>
+          <t>outfit sender old money</t>
         </is>
       </c>
       <c r="C1623" s="2" t="inlineStr">
@@ -69136,12 +69136,12 @@
       <c r="I1623" s="2" t="inlineStr"/>
       <c r="J1623" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-silvio-old-money-1</t>
+          <t>https://tiendasopenmind.com/products/outfit-sender-old-money-2</t>
         </is>
       </c>
       <c r="K1623" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/bb8f82fe-26da-4642-9c7f-2b9a8ed0f413.jpg?v=1792772879</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/804d0344-d2a4-4b97-8bd8-18ecc0ad49c1.jpg?v=1792773209</t>
         </is>
       </c>
       <c r="L1623" s="2" t="n">
@@ -69150,11 +69150,11 @@
     </row>
     <row r="1624">
       <c r="A1624" s="2" t="n">
-        <v>15435994103875</v>
+        <v>15435996692547</v>
       </c>
       <c r="B1624" s="2" t="inlineStr">
         <is>
-          <t>outfit silvio old money</t>
+          <t>outfit sender old money</t>
         </is>
       </c>
       <c r="C1624" s="2" t="inlineStr">
@@ -69178,12 +69178,12 @@
       <c r="I1624" s="2" t="inlineStr"/>
       <c r="J1624" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-silvio-old-money</t>
+          <t>https://tiendasopenmind.com/products/outfit-sender-old-money-1</t>
         </is>
       </c>
       <c r="K1624" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/195fc995-e0d1-498a-924f-54492d142ecc.jpg?v=1792772862</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/5abdaa37-247a-4c94-b0de-d2868d8290af.jpg?v=1792772981</t>
         </is>
       </c>
       <c r="L1624" s="2" t="n">
@@ -69192,11 +69192,11 @@
     </row>
     <row r="1625">
       <c r="A1625" s="2" t="n">
-        <v>15435991613507</v>
+        <v>15435995414595</v>
       </c>
       <c r="B1625" s="2" t="inlineStr">
         <is>
-          <t>outfit sun old money</t>
+          <t>outfit sender old money</t>
         </is>
       </c>
       <c r="C1625" s="2" t="inlineStr">
@@ -69220,12 +69220,12 @@
       <c r="I1625" s="2" t="inlineStr"/>
       <c r="J1625" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-sun-old-money</t>
+          <t>https://tiendasopenmind.com/products/outfit-sender-old-money</t>
         </is>
       </c>
       <c r="K1625" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/8e079267-c65d-471c-9f68-7a88fb49a15e.jpg?v=1792772726</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/98bea179-f1a2-4c98-8055-535a78452666.jpg?v=1792772914</t>
         </is>
       </c>
       <c r="L1625" s="2" t="n">
@@ -69234,11 +69234,11 @@
     </row>
     <row r="1626">
       <c r="A1626" s="2" t="n">
-        <v>15435985584195</v>
+        <v>15435994660931</v>
       </c>
       <c r="B1626" s="2" t="inlineStr">
         <is>
-          <t>outfit your old money</t>
+          <t>outfit silvio old money</t>
         </is>
       </c>
       <c r="C1626" s="2" t="inlineStr">
@@ -69262,12 +69262,12 @@
       <c r="I1626" s="2" t="inlineStr"/>
       <c r="J1626" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-your-old-money-2</t>
+          <t>https://tiendasopenmind.com/products/outfit-silvio-old-money-1</t>
         </is>
       </c>
       <c r="K1626" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/05a5b320-fa50-4de9-8ded-3b189a7cb406_ba421e10-b34a-4a53-b42e-1f05e4562892.jpg?v=1792772485</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/bb8f82fe-26da-4642-9c7f-2b9a8ed0f413.jpg?v=1792772879</t>
         </is>
       </c>
       <c r="L1626" s="2" t="n">
@@ -69276,11 +69276,11 @@
     </row>
     <row r="1627">
       <c r="A1627" s="2" t="n">
-        <v>15435984797763</v>
+        <v>15435994103875</v>
       </c>
       <c r="B1627" s="2" t="inlineStr">
         <is>
-          <t>outfit your old money</t>
+          <t>outfit silvio old money</t>
         </is>
       </c>
       <c r="C1627" s="2" t="inlineStr">
@@ -69304,12 +69304,12 @@
       <c r="I1627" s="2" t="inlineStr"/>
       <c r="J1627" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-your-old-money-1</t>
+          <t>https://tiendasopenmind.com/products/outfit-silvio-old-money</t>
         </is>
       </c>
       <c r="K1627" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/d962843f-01ab-4509-a211-3bfb0e2ffddc.jpg?v=1792772460</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/195fc995-e0d1-498a-924f-54492d142ecc.jpg?v=1792772862</t>
         </is>
       </c>
       <c r="L1627" s="2" t="n">
@@ -69318,11 +69318,11 @@
     </row>
     <row r="1628">
       <c r="A1628" s="2" t="n">
-        <v>15435983913027</v>
+        <v>15435991613507</v>
       </c>
       <c r="B1628" s="2" t="inlineStr">
         <is>
-          <t>outfit your old money</t>
+          <t>outfit sun old money</t>
         </is>
       </c>
       <c r="C1628" s="2" t="inlineStr">
@@ -69346,12 +69346,12 @@
       <c r="I1628" s="2" t="inlineStr"/>
       <c r="J1628" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/outfit-your-old-money</t>
+          <t>https://tiendasopenmind.com/products/outfit-sun-old-money</t>
         </is>
       </c>
       <c r="K1628" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/Outfitninoyourblanco_5EDITARFOTOS.jpg?v=1792862444</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/8e079267-c65d-471c-9f68-7a88fb49a15e.jpg?v=1792772726</t>
         </is>
       </c>
       <c r="L1628" s="2" t="n">
@@ -69360,11 +69360,11 @@
     </row>
     <row r="1629">
       <c r="A1629" s="2" t="n">
-        <v>7673986973763</v>
+        <v>15435985584195</v>
       </c>
       <c r="B1629" s="2" t="inlineStr">
         <is>
-          <t>pantalon drill negro collage outlet</t>
+          <t>outfit your old money</t>
         </is>
       </c>
       <c r="C1629" s="2" t="inlineStr">
@@ -69388,12 +69388,12 @@
       <c r="I1629" s="2" t="inlineStr"/>
       <c r="J1629" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantalon-drill-negro-collage-outlet</t>
+          <t>https://tiendasopenmind.com/products/outfit-your-old-money-2</t>
         </is>
       </c>
       <c r="K1629" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantalondrillnegrocollageoutlet.jpg?v=1780512724</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/05a5b320-fa50-4de9-8ded-3b189a7cb406_ba421e10-b34a-4a53-b42e-1f05e4562892.jpg?v=1792772485</t>
         </is>
       </c>
       <c r="L1629" s="2" t="n">
@@ -69402,11 +69402,11 @@
     </row>
     <row r="1630">
       <c r="A1630" s="2" t="n">
-        <v>7673985826883</v>
+        <v>15435984797763</v>
       </c>
       <c r="B1630" s="2" t="inlineStr">
         <is>
-          <t>pantalon drill negro hombre outlet</t>
+          <t>outfit your old money</t>
         </is>
       </c>
       <c r="C1630" s="2" t="inlineStr">
@@ -69430,12 +69430,12 @@
       <c r="I1630" s="2" t="inlineStr"/>
       <c r="J1630" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantalon-drill-negro-hombre-outlet</t>
+          <t>https://tiendasopenmind.com/products/outfit-your-old-money-1</t>
         </is>
       </c>
       <c r="K1630" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantalondrillnegrohombreoutlet.jpg?v=1780512558</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/d962843f-01ab-4509-a211-3bfb0e2ffddc.jpg?v=1792772460</t>
         </is>
       </c>
       <c r="L1630" s="2" t="n">
@@ -69444,11 +69444,11 @@
     </row>
     <row r="1631">
       <c r="A1631" s="2" t="n">
-        <v>7673986842691</v>
+        <v>15435983913027</v>
       </c>
       <c r="B1631" s="2" t="inlineStr">
         <is>
-          <t>pantalon drill negro niño outlet</t>
+          <t>outfit your old money</t>
         </is>
       </c>
       <c r="C1631" s="2" t="inlineStr">
@@ -69472,12 +69472,12 @@
       <c r="I1631" s="2" t="inlineStr"/>
       <c r="J1631" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantalon-drill-negro-nino-outlet</t>
+          <t>https://tiendasopenmind.com/products/outfit-your-old-money</t>
         </is>
       </c>
       <c r="K1631" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantalondrillnegroninooutlet.jpg?v=1780512675</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/Outfitninoyourblanco_5EDITARFOTOS.jpg?v=1792862444</t>
         </is>
       </c>
       <c r="L1631" s="2" t="n">
@@ -69486,11 +69486,11 @@
     </row>
     <row r="1632">
       <c r="A1632" s="2" t="n">
-        <v>7629779206211</v>
+        <v>7673986973763</v>
       </c>
       <c r="B1632" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta balner hombre</t>
+          <t>pantalon drill negro collage outlet</t>
         </is>
       </c>
       <c r="C1632" s="2" t="inlineStr">
@@ -69514,12 +69514,12 @@
       <c r="I1632" s="2" t="inlineStr"/>
       <c r="J1632" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-balner-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/pantalon-drill-negro-collage-outlet</t>
         </is>
       </c>
       <c r="K1632" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_balner_hombre.jpg?v=1775333687</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantalondrillnegrocollageoutlet.jpg?v=1780512724</t>
         </is>
       </c>
       <c r="L1632" s="2" t="n">
@@ -69528,11 +69528,11 @@
     </row>
     <row r="1633">
       <c r="A1633" s="2" t="n">
-        <v>7629779304515</v>
+        <v>7673985826883</v>
       </c>
       <c r="B1633" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta balner hombre a</t>
+          <t>pantalon drill negro hombre outlet</t>
         </is>
       </c>
       <c r="C1633" s="2" t="inlineStr">
@@ -69556,12 +69556,12 @@
       <c r="I1633" s="2" t="inlineStr"/>
       <c r="J1633" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-balner-hombre-a</t>
+          <t>https://tiendasopenmind.com/products/pantalon-drill-negro-hombre-outlet</t>
         </is>
       </c>
       <c r="K1633" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_balner_hombre_2.jpg?v=1775333753</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantalondrillnegrohombreoutlet.jpg?v=1780512558</t>
         </is>
       </c>
       <c r="L1633" s="2" t="n">
@@ -69570,11 +69570,11 @@
     </row>
     <row r="1634">
       <c r="A1634" s="2" t="n">
-        <v>7629779435587</v>
+        <v>7673986842691</v>
       </c>
       <c r="B1634" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta coluck hombre</t>
+          <t>pantalon drill negro niño outlet</t>
         </is>
       </c>
       <c r="C1634" s="2" t="inlineStr">
@@ -69598,12 +69598,12 @@
       <c r="I1634" s="2" t="inlineStr"/>
       <c r="J1634" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-coluck-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/pantalon-drill-negro-nino-outlet</t>
         </is>
       </c>
       <c r="K1634" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_coluck_hombre.jpg?v=1775333857</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantalondrillnegroninooutlet.jpg?v=1780512675</t>
         </is>
       </c>
       <c r="L1634" s="2" t="n">
@@ -69612,11 +69612,11 @@
     </row>
     <row r="1635">
       <c r="A1635" s="2" t="n">
-        <v>7629779533891</v>
+        <v>7629779206211</v>
       </c>
       <c r="B1635" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta coluck hombre a</t>
+          <t>pantaloneta balner hombre</t>
         </is>
       </c>
       <c r="C1635" s="2" t="inlineStr">
@@ -69640,12 +69640,12 @@
       <c r="I1635" s="2" t="inlineStr"/>
       <c r="J1635" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-coluck-hombre-a</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-balner-hombre-1</t>
         </is>
       </c>
       <c r="K1635" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_coluck_hombre_a.jpg?v=1775333934</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_balner_hombre.jpg?v=1775333687</t>
         </is>
       </c>
       <c r="L1635" s="2" t="n">
@@ -69654,11 +69654,11 @@
     </row>
     <row r="1636">
       <c r="A1636" s="2" t="n">
-        <v>7629779861571</v>
+        <v>7629779304515</v>
       </c>
       <c r="B1636" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta consul hombre</t>
+          <t>pantaloneta balner hombre a</t>
         </is>
       </c>
       <c r="C1636" s="2" t="inlineStr">
@@ -69682,12 +69682,12 @@
       <c r="I1636" s="2" t="inlineStr"/>
       <c r="J1636" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-consul-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-balner-hombre-a</t>
         </is>
       </c>
       <c r="K1636" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_consul_hombre.jpg?v=1775334292</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_balner_hombre_2.jpg?v=1775333753</t>
         </is>
       </c>
       <c r="L1636" s="2" t="n">
@@ -69696,11 +69696,11 @@
     </row>
     <row r="1637">
       <c r="A1637" s="2" t="n">
-        <v>7629779894339</v>
+        <v>7629779435587</v>
       </c>
       <c r="B1637" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta consul hombre a</t>
+          <t>pantaloneta coluck hombre</t>
         </is>
       </c>
       <c r="C1637" s="2" t="inlineStr">
@@ -69724,12 +69724,12 @@
       <c r="I1637" s="2" t="inlineStr"/>
       <c r="J1637" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-consul-hombre-a</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-coluck-hombre-1</t>
         </is>
       </c>
       <c r="K1637" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_consul_hombre_a.jpg?v=1775334378</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_coluck_hombre.jpg?v=1775333857</t>
         </is>
       </c>
       <c r="L1637" s="2" t="n">
@@ -69738,11 +69738,11 @@
     </row>
     <row r="1638">
       <c r="A1638" s="2" t="n">
-        <v>7629779828803</v>
+        <v>7629779533891</v>
       </c>
       <c r="B1638" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta dewnner hombre</t>
+          <t>pantaloneta coluck hombre a</t>
         </is>
       </c>
       <c r="C1638" s="2" t="inlineStr">
@@ -69766,12 +69766,12 @@
       <c r="I1638" s="2" t="inlineStr"/>
       <c r="J1638" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-dewnner-hombre-2</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-coluck-hombre-a</t>
         </is>
       </c>
       <c r="K1638" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_dewnner_hombre_5dcd188f-5e03-47b2-98a5-d9b9ecfea3f5.jpg?v=1775334212</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_coluck_hombre_a.jpg?v=1775333934</t>
         </is>
       </c>
       <c r="L1638" s="2" t="n">
@@ -69780,11 +69780,11 @@
     </row>
     <row r="1639">
       <c r="A1639" s="2" t="n">
-        <v>7629779107907</v>
+        <v>7629779861571</v>
       </c>
       <c r="B1639" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta dewnner hombre</t>
+          <t>pantaloneta consul hombre</t>
         </is>
       </c>
       <c r="C1639" s="2" t="inlineStr">
@@ -69808,12 +69808,12 @@
       <c r="I1639" s="2" t="inlineStr"/>
       <c r="J1639" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-dewnner-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-consul-hombre-1</t>
         </is>
       </c>
       <c r="K1639" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_dewnner_hombre.jpg?v=1775333551</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_consul_hombre.jpg?v=1775334292</t>
         </is>
       </c>
       <c r="L1639" s="2" t="n">
@@ -69822,11 +69822,11 @@
     </row>
     <row r="1640">
       <c r="A1640" s="2" t="n">
-        <v>7629779173443</v>
+        <v>7629779894339</v>
       </c>
       <c r="B1640" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta one hombre</t>
+          <t>pantaloneta consul hombre a</t>
         </is>
       </c>
       <c r="C1640" s="2" t="inlineStr">
@@ -69850,12 +69850,12 @@
       <c r="I1640" s="2" t="inlineStr"/>
       <c r="J1640" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-one-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-consul-hombre-a</t>
         </is>
       </c>
       <c r="K1640" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_one_hombre.jpg?v=1775333612</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_consul_hombre_a.jpg?v=1775334378</t>
         </is>
       </c>
       <c r="L1640" s="2" t="n">
@@ -69864,11 +69864,11 @@
     </row>
     <row r="1641">
       <c r="A1641" s="2" t="n">
-        <v>7629779632195</v>
+        <v>7629779828803</v>
       </c>
       <c r="B1641" s="2" t="inlineStr">
         <is>
-          <t>pantaloneta one hombre a</t>
+          <t>pantaloneta dewnner hombre</t>
         </is>
       </c>
       <c r="C1641" s="2" t="inlineStr">
@@ -69892,12 +69892,12 @@
       <c r="I1641" s="2" t="inlineStr"/>
       <c r="J1641" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/pantaloneta-one-hombre-a</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-dewnner-hombre-2</t>
         </is>
       </c>
       <c r="K1641" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_one_hombre_a.jpg?v=1775334057</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_dewnner_hombre_5dcd188f-5e03-47b2-98a5-d9b9ecfea3f5.jpg?v=1775334212</t>
         </is>
       </c>
       <c r="L1641" s="2" t="n">
@@ -69906,11 +69906,11 @@
     </row>
     <row r="1642">
       <c r="A1642" s="2" t="n">
-        <v>7817790423107</v>
+        <v>7629779107907</v>
       </c>
       <c r="B1642" s="2" t="inlineStr">
         <is>
-          <t>sudadera Alaba collage hombre</t>
+          <t>pantaloneta dewnner hombre</t>
         </is>
       </c>
       <c r="C1642" s="2" t="inlineStr">
@@ -69934,12 +69934,12 @@
       <c r="I1642" s="2" t="inlineStr"/>
       <c r="J1642" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-alaba-collage-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-dewnner-hombre-1</t>
         </is>
       </c>
       <c r="K1642" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.20AM_1.jpg?v=1788207949</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_dewnner_hombre.jpg?v=1775333551</t>
         </is>
       </c>
       <c r="L1642" s="2" t="n">
@@ -69948,11 +69948,11 @@
     </row>
     <row r="1643">
       <c r="A1643" s="2" t="n">
-        <v>7817789931587</v>
+        <v>7629779173443</v>
       </c>
       <c r="B1643" s="2" t="inlineStr">
         <is>
-          <t>sudadera Alaba mix hombre</t>
+          <t>pantaloneta one hombre</t>
         </is>
       </c>
       <c r="C1643" s="2" t="inlineStr">
@@ -69976,12 +69976,12 @@
       <c r="I1643" s="2" t="inlineStr"/>
       <c r="J1643" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-alaba-mix-hombre</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-one-hombre-1</t>
         </is>
       </c>
       <c r="K1643" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.21AM.jpg?v=1788207857</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_one_hombre.jpg?v=1775333612</t>
         </is>
       </c>
       <c r="L1643" s="2" t="n">
@@ -69990,11 +69990,11 @@
     </row>
     <row r="1644">
       <c r="A1644" s="2" t="n">
-        <v>7817790128195</v>
+        <v>7629779632195</v>
       </c>
       <c r="B1644" s="2" t="inlineStr">
         <is>
-          <t>sudadera Alaba negro hombre</t>
+          <t>pantaloneta one hombre a</t>
         </is>
       </c>
       <c r="C1644" s="2" t="inlineStr">
@@ -70018,12 +70018,12 @@
       <c r="I1644" s="2" t="inlineStr"/>
       <c r="J1644" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-alaba-negro-hombre</t>
+          <t>https://tiendasopenmind.com/products/pantaloneta-one-hombre-a</t>
         </is>
       </c>
       <c r="K1644" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.20AM.jpg?v=1788207915</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/pantaloneta_one_hombre_a.jpg?v=1775334057</t>
         </is>
       </c>
       <c r="L1644" s="2" t="n">
@@ -70032,11 +70032,11 @@
     </row>
     <row r="1645">
       <c r="A1645" s="2" t="n">
-        <v>7817795600451</v>
+        <v>7817790423107</v>
       </c>
       <c r="B1645" s="2" t="inlineStr">
         <is>
-          <t>sudadera Thibaut collage hombre</t>
+          <t>sudadera Alaba collage hombre</t>
         </is>
       </c>
       <c r="C1645" s="2" t="inlineStr">
@@ -70060,12 +70060,12 @@
       <c r="I1645" s="2" t="inlineStr"/>
       <c r="J1645" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-thibaut-collage-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/sudadera-alaba-collage-hombre-1</t>
         </is>
       </c>
       <c r="K1645" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.31AM_1.jpg?v=1788208198</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.20AM_1.jpg?v=1788207949</t>
         </is>
       </c>
       <c r="L1645" s="2" t="n">
@@ -70074,11 +70074,11 @@
     </row>
     <row r="1646">
       <c r="A1646" s="2" t="n">
-        <v>7817794191427</v>
+        <v>7817789931587</v>
       </c>
       <c r="B1646" s="2" t="inlineStr">
         <is>
-          <t>sudadera Thibaut gris o. hombre</t>
+          <t>sudadera Alaba mix hombre</t>
         </is>
       </c>
       <c r="C1646" s="2" t="inlineStr">
@@ -70102,12 +70102,12 @@
       <c r="I1646" s="2" t="inlineStr"/>
       <c r="J1646" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-thibaut-gris-o-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/sudadera-alaba-mix-hombre</t>
         </is>
       </c>
       <c r="K1646" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.32AM.jpg?v=1788208166</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.21AM.jpg?v=1788207857</t>
         </is>
       </c>
       <c r="L1646" s="2" t="n">
@@ -70116,11 +70116,11 @@
     </row>
     <row r="1647">
       <c r="A1647" s="2" t="n">
-        <v>7817793503299</v>
+        <v>7817790128195</v>
       </c>
       <c r="B1647" s="2" t="inlineStr">
         <is>
-          <t>sudadera Thibaut negro hombre</t>
+          <t>sudadera Alaba negro hombre</t>
         </is>
       </c>
       <c r="C1647" s="2" t="inlineStr">
@@ -70144,12 +70144,12 @@
       <c r="I1647" s="2" t="inlineStr"/>
       <c r="J1647" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-thibaut-negro-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/sudadera-alaba-negro-hombre</t>
         </is>
       </c>
       <c r="K1647" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.31AM.jpg?v=1788208120</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.20AM.jpg?v=1788207915</t>
         </is>
       </c>
       <c r="L1647" s="2" t="n">
@@ -70158,11 +70158,11 @@
     </row>
     <row r="1648">
       <c r="A1648" s="2" t="n">
-        <v>7817789505603</v>
+        <v>7817795600451</v>
       </c>
       <c r="B1648" s="2" t="inlineStr">
         <is>
-          <t>sudadera Trend collage hombre</t>
+          <t>sudadera Thibaut collage hombre</t>
         </is>
       </c>
       <c r="C1648" s="2" t="inlineStr">
@@ -70186,12 +70186,12 @@
       <c r="I1648" s="2" t="inlineStr"/>
       <c r="J1648" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-trend-collage-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/sudadera-thibaut-collage-hombre-1</t>
         </is>
       </c>
       <c r="K1648" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.06AM_1.jpg?v=1788207810</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.31AM_1.jpg?v=1788208198</t>
         </is>
       </c>
       <c r="L1648" s="2" t="n">
@@ -70200,11 +70200,11 @@
     </row>
     <row r="1649">
       <c r="A1649" s="2" t="n">
-        <v>7817788719171</v>
+        <v>7817794191427</v>
       </c>
       <c r="B1649" s="2" t="inlineStr">
         <is>
-          <t>sudadera Trend gis c. hombre</t>
+          <t>sudadera Thibaut gris o. hombre</t>
         </is>
       </c>
       <c r="C1649" s="2" t="inlineStr">
@@ -70228,12 +70228,12 @@
       <c r="I1649" s="2" t="inlineStr"/>
       <c r="J1649" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-trend-gis-c-hombre</t>
+          <t>https://tiendasopenmind.com/products/sudadera-thibaut-gris-o-hombre-1</t>
         </is>
       </c>
       <c r="K1649" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.05AM.jpg?v=1788207669</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.32AM.jpg?v=1788208166</t>
         </is>
       </c>
       <c r="L1649" s="2" t="n">
@@ -70242,11 +70242,11 @@
     </row>
     <row r="1650">
       <c r="A1650" s="2" t="n">
-        <v>7817789014083</v>
+        <v>7817793503299</v>
       </c>
       <c r="B1650" s="2" t="inlineStr">
         <is>
-          <t>sudadera Trend sable hombre</t>
+          <t>sudadera Thibaut negro hombre</t>
         </is>
       </c>
       <c r="C1650" s="2" t="inlineStr">
@@ -70270,12 +70270,12 @@
       <c r="I1650" s="2" t="inlineStr"/>
       <c r="J1650" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-trend-sable-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/sudadera-thibaut-negro-hombre-1</t>
         </is>
       </c>
       <c r="K1650" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.06AM.jpg?v=1788207717</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.31AM.jpg?v=1788208120</t>
         </is>
       </c>
       <c r="L1650" s="2" t="n">
@@ -70284,11 +70284,11 @@
     </row>
     <row r="1651">
       <c r="A1651" s="2" t="n">
-        <v>7817785540675</v>
+        <v>7817789505603</v>
       </c>
       <c r="B1651" s="2" t="inlineStr">
         <is>
-          <t>sudadera rudiger gis hombre</t>
+          <t>sudadera Trend collage hombre</t>
         </is>
       </c>
       <c r="C1651" s="2" t="inlineStr">
@@ -70312,12 +70312,12 @@
       <c r="I1651" s="2" t="inlineStr"/>
       <c r="J1651" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/sudadera-jogger-rudiger-gis-hombre</t>
+          <t>https://tiendasopenmind.com/products/sudadera-trend-collage-hombre-1</t>
         </is>
       </c>
       <c r="K1651" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.27.49AM.jpg?v=1788206837</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.06AM_1.jpg?v=1788207810</t>
         </is>
       </c>
       <c r="L1651" s="2" t="n">
@@ -70326,11 +70326,11 @@
     </row>
     <row r="1652">
       <c r="A1652" s="2" t="n">
-        <v>7663131787331</v>
+        <v>7817788719171</v>
       </c>
       <c r="B1652" s="2" t="inlineStr">
         <is>
-          <t>total look adrano niño</t>
+          <t>sudadera Trend gis c. hombre</t>
         </is>
       </c>
       <c r="C1652" s="2" t="inlineStr">
@@ -70354,12 +70354,12 @@
       <c r="I1652" s="2" t="inlineStr"/>
       <c r="J1652" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-adrano-nino</t>
+          <t>https://tiendasopenmind.com/products/sudadera-trend-gis-c-hombre</t>
         </is>
       </c>
       <c r="K1652" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKADRANO_5EDITARFOTOS.jpg?v=1792853339</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.05AM.jpg?v=1788207669</t>
         </is>
       </c>
       <c r="L1652" s="2" t="n">
@@ -70368,11 +70368,11 @@
     </row>
     <row r="1653">
       <c r="A1653" s="2" t="n">
-        <v>7642257719363</v>
+        <v>7817789014083</v>
       </c>
       <c r="B1653" s="2" t="inlineStr">
         <is>
-          <t>total look battista collage hombre</t>
+          <t>sudadera Trend sable hombre</t>
         </is>
       </c>
       <c r="C1653" s="2" t="inlineStr">
@@ -70396,12 +70396,12 @@
       <c r="I1653" s="2" t="inlineStr"/>
       <c r="J1653" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-battista-collage</t>
+          <t>https://tiendasopenmind.com/products/sudadera-trend-sable-hombre-1</t>
         </is>
       </c>
       <c r="K1653" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.17.44PM.jpg?v=1784920988</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.28.06AM.jpg?v=1788207717</t>
         </is>
       </c>
       <c r="L1653" s="2" t="n">
@@ -70410,11 +70410,11 @@
     </row>
     <row r="1654">
       <c r="A1654" s="2" t="n">
-        <v>7642258931779</v>
+        <v>7817785540675</v>
       </c>
       <c r="B1654" s="2" t="inlineStr">
         <is>
-          <t>total look battista natural hombre</t>
+          <t>sudadera rudiger gis hombre</t>
         </is>
       </c>
       <c r="C1654" s="2" t="inlineStr">
@@ -70438,12 +70438,12 @@
       <c r="I1654" s="2" t="inlineStr"/>
       <c r="J1654" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-battista-natural-hombre</t>
+          <t>https://tiendasopenmind.com/products/sudadera-jogger-rudiger-gis-hombre</t>
         </is>
       </c>
       <c r="K1654" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.17.44PM_2.jpg?v=1784921050</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-08-13at11.27.49AM.jpg?v=1788206837</t>
         </is>
       </c>
       <c r="L1654" s="2" t="n">
@@ -70452,11 +70452,11 @@
     </row>
     <row r="1655">
       <c r="A1655" s="2" t="n">
-        <v>7642260373571</v>
+        <v>7663131787331</v>
       </c>
       <c r="B1655" s="2" t="inlineStr">
         <is>
-          <t>total look battista negro hombre</t>
+          <t>total look adrano niño</t>
         </is>
       </c>
       <c r="C1655" s="2" t="inlineStr">
@@ -70480,12 +70480,12 @@
       <c r="I1655" s="2" t="inlineStr"/>
       <c r="J1655" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-battista-negro-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-adrano-nino</t>
         </is>
       </c>
       <c r="K1655" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.17.44PM_1.jpg?v=1784921022</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKADRANO_5EDITARFOTOS.jpg?v=1792853339</t>
         </is>
       </c>
       <c r="L1655" s="2" t="n">
@@ -70494,11 +70494,11 @@
     </row>
     <row r="1656">
       <c r="A1656" s="2" t="n">
-        <v>10272920305731</v>
+        <v>7642257719363</v>
       </c>
       <c r="B1656" s="2" t="inlineStr">
         <is>
-          <t>total look big niño</t>
+          <t>total look battista collage hombre</t>
         </is>
       </c>
       <c r="C1656" s="2" t="inlineStr">
@@ -70522,12 +70522,12 @@
       <c r="I1656" s="2" t="inlineStr"/>
       <c r="J1656" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-big-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-battista-collage</t>
         </is>
       </c>
       <c r="K1656" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/big_f8600221-7d17-4c4d-ae23-d48a9a2f2185.jpg?v=1790466417</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.17.44PM.jpg?v=1784920988</t>
         </is>
       </c>
       <c r="L1656" s="2" t="n">
@@ -70536,11 +70536,11 @@
     </row>
     <row r="1657">
       <c r="A1657" s="2" t="n">
-        <v>15436710969411</v>
+        <v>7642258931779</v>
       </c>
       <c r="B1657" s="2" t="inlineStr">
         <is>
-          <t>total look bolzano collage</t>
+          <t>total look battista natural hombre</t>
         </is>
       </c>
       <c r="C1657" s="2" t="inlineStr">
@@ -70564,12 +70564,12 @@
       <c r="I1657" s="2" t="inlineStr"/>
       <c r="J1657" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-bolzano-collage</t>
+          <t>https://tiendasopenmind.com/products/total-look-battista-natural-hombre</t>
         </is>
       </c>
       <c r="K1657" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKBOLZANOCOLLAGE_5EDITARFOTOS.jpg?v=1792790249</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.17.44PM_2.jpg?v=1784921050</t>
         </is>
       </c>
       <c r="L1657" s="2" t="n">
@@ -70578,11 +70578,11 @@
     </row>
     <row r="1658">
       <c r="A1658" s="2" t="n">
-        <v>7781185617987</v>
+        <v>7642260373571</v>
       </c>
       <c r="B1658" s="2" t="inlineStr">
         <is>
-          <t>total look bolzano hombre</t>
+          <t>total look battista negro hombre</t>
         </is>
       </c>
       <c r="C1658" s="2" t="inlineStr">
@@ -70606,12 +70606,12 @@
       <c r="I1658" s="2" t="inlineStr"/>
       <c r="J1658" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-bolzano-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/total-look-battista-negro-hombre</t>
         </is>
       </c>
       <c r="K1658" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/bolzano_a5a8e96f-138a-406f-b399-406d9dbb9ead.jpg?v=1790462726</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.17.44PM_1.jpg?v=1784921022</t>
         </is>
       </c>
       <c r="L1658" s="2" t="n">
@@ -70620,11 +70620,11 @@
     </row>
     <row r="1659">
       <c r="A1659" s="2" t="n">
-        <v>15436715950147</v>
+        <v>10272920305731</v>
       </c>
       <c r="B1659" s="2" t="inlineStr">
         <is>
-          <t>total look bolzano kids</t>
+          <t>total look big niño</t>
         </is>
       </c>
       <c r="C1659" s="2" t="inlineStr">
@@ -70648,12 +70648,12 @@
       <c r="I1659" s="2" t="inlineStr"/>
       <c r="J1659" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-bolzano-kids</t>
+          <t>https://tiendasopenmind.com/products/total-look-big-nino</t>
         </is>
       </c>
       <c r="K1659" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKBOLZANONINAEDITARFOTOS_5EDITARFOTOS.jpg?v=1792791422</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/big_f8600221-7d17-4c4d-ae23-d48a9a2f2185.jpg?v=1790466417</t>
         </is>
       </c>
       <c r="L1659" s="2" t="n">
@@ -70662,11 +70662,11 @@
     </row>
     <row r="1660">
       <c r="A1660" s="2" t="n">
-        <v>15436716015683</v>
+        <v>15436710969411</v>
       </c>
       <c r="B1660" s="2" t="inlineStr">
         <is>
-          <t>total look bolzano niño</t>
+          <t>total look bolzano collage</t>
         </is>
       </c>
       <c r="C1660" s="2" t="inlineStr">
@@ -70690,12 +70690,12 @@
       <c r="I1660" s="2" t="inlineStr"/>
       <c r="J1660" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-bolzano-nino-1</t>
+          <t>https://tiendasopenmind.com/products/total-look-bolzano-collage</t>
         </is>
       </c>
       <c r="K1660" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKBOLZANONINOEDITARFOTOS_5EDITARFOTOS_5EDITARFOTOS.jpg?v=1792791480</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKBOLZANOCOLLAGE_5EDITARFOTOS.jpg?v=1792790249</t>
         </is>
       </c>
       <c r="L1660" s="2" t="n">
@@ -70704,11 +70704,11 @@
     </row>
     <row r="1661">
       <c r="A1661" s="2" t="n">
-        <v>7644342878275</v>
+        <v>7781185617987</v>
       </c>
       <c r="B1661" s="2" t="inlineStr">
         <is>
-          <t>total look brandon astro hombre</t>
+          <t>total look bolzano hombre</t>
         </is>
       </c>
       <c r="C1661" s="2" t="inlineStr">
@@ -70732,12 +70732,12 @@
       <c r="I1661" s="2" t="inlineStr"/>
       <c r="J1661" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-brandon-astro-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-bolzano-hombre-1</t>
         </is>
       </c>
       <c r="K1661" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.51AM_1.jpg?v=1784821634</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/bolzano_a5a8e96f-138a-406f-b399-406d9dbb9ead.jpg?v=1790462726</t>
         </is>
       </c>
       <c r="L1661" s="2" t="n">
@@ -70746,11 +70746,11 @@
     </row>
     <row r="1662">
       <c r="A1662" s="2" t="n">
-        <v>7644343074883</v>
+        <v>15436715950147</v>
       </c>
       <c r="B1662" s="2" t="inlineStr">
         <is>
-          <t>total look brandon collage hombre</t>
+          <t>total look bolzano kids</t>
         </is>
       </c>
       <c r="C1662" s="2" t="inlineStr">
@@ -70774,12 +70774,12 @@
       <c r="I1662" s="2" t="inlineStr"/>
       <c r="J1662" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-brandon-collage-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-bolzano-kids</t>
         </is>
       </c>
       <c r="K1662" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.50AM.jpg?v=1784821536</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKBOLZANONINAEDITARFOTOS_5EDITARFOTOS.jpg?v=1792791422</t>
         </is>
       </c>
       <c r="L1662" s="2" t="n">
@@ -70788,11 +70788,11 @@
     </row>
     <row r="1663">
       <c r="A1663" s="2" t="n">
-        <v>7644342026307</v>
+        <v>15436716015683</v>
       </c>
       <c r="B1663" s="2" t="inlineStr">
         <is>
-          <t>total look brandon gris c hombre</t>
+          <t>total look bolzano niño</t>
         </is>
       </c>
       <c r="C1663" s="2" t="inlineStr">
@@ -70816,12 +70816,12 @@
       <c r="I1663" s="2" t="inlineStr"/>
       <c r="J1663" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-brandon-gris-c-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-bolzano-nino-1</t>
         </is>
       </c>
       <c r="K1663" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.51AM.jpg?v=1784821572</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/TOTALLOOKBOLZANONINOEDITARFOTOS_5EDITARFOTOS_5EDITARFOTOS.jpg?v=1792791480</t>
         </is>
       </c>
       <c r="L1663" s="2" t="n">
@@ -70830,11 +70830,11 @@
     </row>
     <row r="1664">
       <c r="A1664" s="2" t="n">
-        <v>7781185716291</v>
+        <v>7644342878275</v>
       </c>
       <c r="B1664" s="2" t="inlineStr">
         <is>
-          <t>total look cantu hombre</t>
+          <t>total look brandon astro hombre</t>
         </is>
       </c>
       <c r="C1664" s="2" t="inlineStr">
@@ -70858,12 +70858,12 @@
       <c r="I1664" s="2" t="inlineStr"/>
       <c r="J1664" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-cantu-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/total-look-brandon-astro-hombre</t>
         </is>
       </c>
       <c r="K1664" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-22at9.53.38AM.jpg?v=1785610271</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.51AM_1.jpg?v=1784821634</t>
         </is>
       </c>
       <c r="L1664" s="2" t="n">
@@ -70872,11 +70872,11 @@
     </row>
     <row r="1665">
       <c r="A1665" s="2" t="n">
-        <v>7669785460803</v>
+        <v>7644343074883</v>
       </c>
       <c r="B1665" s="2" t="inlineStr">
         <is>
-          <t>total look cento hombre</t>
+          <t>total look brandon collage hombre</t>
         </is>
       </c>
       <c r="C1665" s="2" t="inlineStr">
@@ -70900,12 +70900,12 @@
       <c r="I1665" s="2" t="inlineStr"/>
       <c r="J1665" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-cento-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/total-look-brandon-collage-hombre</t>
         </is>
       </c>
       <c r="K1665" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-29at4.22.22PM.jpg?v=1785603517</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.50AM.jpg?v=1784821536</t>
         </is>
       </c>
       <c r="L1665" s="2" t="n">
@@ -70914,11 +70914,11 @@
     </row>
     <row r="1666">
       <c r="A1666" s="2" t="n">
-        <v>7642233176131</v>
+        <v>7644342026307</v>
       </c>
       <c r="B1666" s="2" t="inlineStr">
         <is>
-          <t>total look cooper astro hombre</t>
+          <t>total look brandon gris c hombre</t>
         </is>
       </c>
       <c r="C1666" s="2" t="inlineStr">
@@ -70942,12 +70942,12 @@
       <c r="I1666" s="2" t="inlineStr"/>
       <c r="J1666" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-cooper-astro-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-brandon-gris-c-hombre</t>
         </is>
       </c>
       <c r="K1666" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookcooperastrohombre.jpg?v=1776703402</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.51AM.jpg?v=1784821572</t>
         </is>
       </c>
       <c r="L1666" s="2" t="n">
@@ -70956,11 +70956,11 @@
     </row>
     <row r="1667">
       <c r="A1667" s="2" t="n">
-        <v>7642232356931</v>
+        <v>7781185716291</v>
       </c>
       <c r="B1667" s="2" t="inlineStr">
         <is>
-          <t>total look cooper collage hombre</t>
+          <t>total look cantu hombre</t>
         </is>
       </c>
       <c r="C1667" s="2" t="inlineStr">
@@ -70984,12 +70984,12 @@
       <c r="I1667" s="2" t="inlineStr"/>
       <c r="J1667" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-cooper-collage-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-cantu-hombre-1</t>
         </is>
       </c>
       <c r="K1667" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookcoopercollagehombre.jpg?v=1776703310</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-22at9.53.38AM.jpg?v=1785610271</t>
         </is>
       </c>
       <c r="L1667" s="2" t="n">
@@ -70998,11 +70998,11 @@
     </row>
     <row r="1668">
       <c r="A1668" s="2" t="n">
-        <v>7642232848451</v>
+        <v>7669785460803</v>
       </c>
       <c r="B1668" s="2" t="inlineStr">
         <is>
-          <t>total look cooper negro hombre</t>
+          <t>total look cento hombre</t>
         </is>
       </c>
       <c r="C1668" s="2" t="inlineStr">
@@ -71026,12 +71026,12 @@
       <c r="I1668" s="2" t="inlineStr"/>
       <c r="J1668" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-cooper-negro-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-cento-hombre-1</t>
         </is>
       </c>
       <c r="K1668" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.18.08PM.jpg?v=1784921561</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-29at4.22.22PM.jpg?v=1785603517</t>
         </is>
       </c>
       <c r="L1668" s="2" t="n">
@@ -71040,11 +71040,11 @@
     </row>
     <row r="1669">
       <c r="A1669" s="2" t="n">
-        <v>10272920043587</v>
+        <v>7642233176131</v>
       </c>
       <c r="B1669" s="2" t="inlineStr">
         <is>
-          <t>total look crib niño</t>
+          <t>total look cooper astro hombre</t>
         </is>
       </c>
       <c r="C1669" s="2" t="inlineStr">
@@ -71068,12 +71068,12 @@
       <c r="I1669" s="2" t="inlineStr"/>
       <c r="J1669" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-crib-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-cooper-astro-hombre</t>
         </is>
       </c>
       <c r="K1669" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/crib_0de851d6-8397-4c84-ab38-c8ce3764d263.jpg?v=1790466109</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookcooperastrohombre.jpg?v=1776703402</t>
         </is>
       </c>
       <c r="L1669" s="2" t="n">
@@ -71082,11 +71082,11 @@
     </row>
     <row r="1670">
       <c r="A1670" s="2" t="n">
-        <v>10272920010819</v>
+        <v>7642232356931</v>
       </c>
       <c r="B1670" s="2" t="inlineStr">
         <is>
-          <t>total look dip niño</t>
+          <t>total look cooper collage hombre</t>
         </is>
       </c>
       <c r="C1670" s="2" t="inlineStr">
@@ -71110,12 +71110,12 @@
       <c r="I1670" s="2" t="inlineStr"/>
       <c r="J1670" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-dip-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-cooper-collage-hombre</t>
         </is>
       </c>
       <c r="K1670" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/dip_36f5a78e-b680-4a6e-bc16-d28902c5067b.jpg?v=1790466060</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookcoopercollagehombre.jpg?v=1776703310</t>
         </is>
       </c>
       <c r="L1670" s="2" t="n">
@@ -71124,11 +71124,11 @@
     </row>
     <row r="1671">
       <c r="A1671" s="2" t="n">
-        <v>7653682446403</v>
+        <v>7642232848451</v>
       </c>
       <c r="B1671" s="2" t="inlineStr">
         <is>
-          <t>total look fonze astro hombre</t>
+          <t>total look cooper negro hombre</t>
         </is>
       </c>
       <c r="C1671" s="2" t="inlineStr">
@@ -71152,12 +71152,12 @@
       <c r="I1671" s="2" t="inlineStr"/>
       <c r="J1671" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-fonze-astro-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-cooper-negro-hombre</t>
         </is>
       </c>
       <c r="K1671" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.09AM_1.jpg?v=1784821896</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-18at2.18.08PM.jpg?v=1784921561</t>
         </is>
       </c>
       <c r="L1671" s="2" t="n">
@@ -71166,11 +71166,11 @@
     </row>
     <row r="1672">
       <c r="A1672" s="2" t="n">
-        <v>7653682217027</v>
+        <v>10272920043587</v>
       </c>
       <c r="B1672" s="2" t="inlineStr">
         <is>
-          <t>total look fonze collage hombre</t>
+          <t>total look crib niño</t>
         </is>
       </c>
       <c r="C1672" s="2" t="inlineStr">
@@ -71194,12 +71194,12 @@
       <c r="I1672" s="2" t="inlineStr"/>
       <c r="J1672" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-fonze-collage-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-crib-nino</t>
         </is>
       </c>
       <c r="K1672" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.08AM.jpg?v=1784821741</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/crib_0de851d6-8397-4c84-ab38-c8ce3764d263.jpg?v=1790466109</t>
         </is>
       </c>
       <c r="L1672" s="2" t="n">
@@ -71208,11 +71208,11 @@
     </row>
     <row r="1673">
       <c r="A1673" s="2" t="n">
-        <v>7653682544707</v>
+        <v>10272920010819</v>
       </c>
       <c r="B1673" s="2" t="inlineStr">
         <is>
-          <t>total look fonze natural hombre</t>
+          <t>total look dip niño</t>
         </is>
       </c>
       <c r="C1673" s="2" t="inlineStr">
@@ -71236,12 +71236,12 @@
       <c r="I1673" s="2" t="inlineStr"/>
       <c r="J1673" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-fonze-natural-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-dip-nino</t>
         </is>
       </c>
       <c r="K1673" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.08AM_1.jpg?v=1784821788</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/dip_36f5a78e-b680-4a6e-bc16-d28902c5067b.jpg?v=1790466060</t>
         </is>
       </c>
       <c r="L1673" s="2" t="n">
@@ -71250,11 +71250,11 @@
     </row>
     <row r="1674">
       <c r="A1674" s="2" t="n">
-        <v>7653682479171</v>
+        <v>7653682446403</v>
       </c>
       <c r="B1674" s="2" t="inlineStr">
         <is>
-          <t>total look fonze negro hombre</t>
+          <t>total look fonze astro hombre</t>
         </is>
       </c>
       <c r="C1674" s="2" t="inlineStr">
@@ -71278,12 +71278,12 @@
       <c r="I1674" s="2" t="inlineStr"/>
       <c r="J1674" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-fonze-negro-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-fonze-astro-hombre</t>
         </is>
       </c>
       <c r="K1674" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.09AM.jpg?v=1784821825</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.09AM_1.jpg?v=1784821896</t>
         </is>
       </c>
       <c r="L1674" s="2" t="n">
@@ -71292,11 +71292,11 @@
     </row>
     <row r="1675">
       <c r="A1675" s="2" t="n">
-        <v>10272919978051</v>
+        <v>7653682217027</v>
       </c>
       <c r="B1675" s="2" t="inlineStr">
         <is>
-          <t>total look funk niño</t>
+          <t>total look fonze collage hombre</t>
         </is>
       </c>
       <c r="C1675" s="2" t="inlineStr">
@@ -71320,12 +71320,12 @@
       <c r="I1675" s="2" t="inlineStr"/>
       <c r="J1675" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-funk-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-fonze-collage-hombre</t>
         </is>
       </c>
       <c r="K1675" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/funk_93524947-9d90-4978-94e4-51855630365d.jpg?v=1790466025</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.08AM.jpg?v=1784821741</t>
         </is>
       </c>
       <c r="L1675" s="2" t="n">
@@ -71334,11 +71334,11 @@
     </row>
     <row r="1676">
       <c r="A1676" s="2" t="n">
-        <v>15436722700355</v>
+        <v>7653682544707</v>
       </c>
       <c r="B1676" s="2" t="inlineStr">
         <is>
-          <t>total look glaviano collage</t>
+          <t>total look fonze natural hombre</t>
         </is>
       </c>
       <c r="C1676" s="2" t="inlineStr">
@@ -71362,12 +71362,12 @@
       <c r="I1676" s="2" t="inlineStr"/>
       <c r="J1676" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-glaviano-collage</t>
+          <t>https://tiendasopenmind.com/products/total-look-fonze-natural-hombre</t>
         </is>
       </c>
       <c r="K1676" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookglaviano_5EDITARFOTOS.jpg?v=1792793277</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.08AM_1.jpg?v=1784821788</t>
         </is>
       </c>
       <c r="L1676" s="2" t="n">
@@ -71376,11 +71376,11 @@
     </row>
     <row r="1677">
       <c r="A1677" s="2" t="n">
-        <v>7669787000899</v>
+        <v>7653682479171</v>
       </c>
       <c r="B1677" s="2" t="inlineStr">
         <is>
-          <t>total look glaviano hombre</t>
+          <t>total look fonze negro hombre</t>
         </is>
       </c>
       <c r="C1677" s="2" t="inlineStr">
@@ -71404,12 +71404,12 @@
       <c r="I1677" s="2" t="inlineStr"/>
       <c r="J1677" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-glaviano-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-fonze-negro-hombre</t>
         </is>
       </c>
       <c r="K1677" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/glaviano.jpg?v=1790462099</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.34.09AM.jpg?v=1784821825</t>
         </is>
       </c>
       <c r="L1677" s="2" t="n">
@@ -71418,11 +71418,11 @@
     </row>
     <row r="1678">
       <c r="A1678" s="2" t="n">
-        <v>15436722831427</v>
+        <v>10272919978051</v>
       </c>
       <c r="B1678" s="2" t="inlineStr">
         <is>
-          <t>total look glaviano niña</t>
+          <t>total look funk niño</t>
         </is>
       </c>
       <c r="C1678" s="2" t="inlineStr">
@@ -71446,12 +71446,12 @@
       <c r="I1678" s="2" t="inlineStr"/>
       <c r="J1678" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-glaviano-nina</t>
+          <t>https://tiendasopenmind.com/products/total-look-funk-nino</t>
         </is>
       </c>
       <c r="K1678" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookglavianonina_5EDITARFOTOS.jpg?v=1792793335</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/funk_93524947-9d90-4978-94e4-51855630365d.jpg?v=1790466025</t>
         </is>
       </c>
       <c r="L1678" s="2" t="n">
@@ -71460,11 +71460,11 @@
     </row>
     <row r="1679">
       <c r="A1679" s="2" t="n">
-        <v>15436722733123</v>
+        <v>15436722700355</v>
       </c>
       <c r="B1679" s="2" t="inlineStr">
         <is>
-          <t>total look glaviano niño</t>
+          <t>total look glaviano collage</t>
         </is>
       </c>
       <c r="C1679" s="2" t="inlineStr">
@@ -71488,12 +71488,12 @@
       <c r="I1679" s="2" t="inlineStr"/>
       <c r="J1679" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-glaviano-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-glaviano-collage</t>
         </is>
       </c>
       <c r="K1679" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookglavianonino_5EDITARFOTOS.jpg?v=1792793310</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookglaviano_5EDITARFOTOS.jpg?v=1792793277</t>
         </is>
       </c>
       <c r="L1679" s="2" t="n">
@@ -71502,11 +71502,11 @@
     </row>
     <row r="1680">
       <c r="A1680" s="2" t="n">
-        <v>15436723028035</v>
+        <v>7669787000899</v>
       </c>
       <c r="B1680" s="2" t="inlineStr">
         <is>
-          <t>total look jostin niño</t>
+          <t>total look glaviano hombre</t>
         </is>
       </c>
       <c r="C1680" s="2" t="inlineStr">
@@ -71530,12 +71530,12 @@
       <c r="I1680" s="2" t="inlineStr"/>
       <c r="J1680" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-jostin-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-glaviano-hombre</t>
         </is>
       </c>
       <c r="K1680" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/b0c0a9bb-34b3-40b9-8008-ef2f75dd06ed.jpg?v=1792793498</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/glaviano.jpg?v=1790462099</t>
         </is>
       </c>
       <c r="L1680" s="2" t="n">
@@ -71544,11 +71544,11 @@
     </row>
     <row r="1681">
       <c r="A1681" s="2" t="n">
-        <v>7643891138627</v>
+        <v>15436722831427</v>
       </c>
       <c r="B1681" s="2" t="inlineStr">
         <is>
-          <t>total look nolan azul c hombre</t>
+          <t>total look glaviano niña</t>
         </is>
       </c>
       <c r="C1681" s="2" t="inlineStr">
@@ -71572,12 +71572,12 @@
       <c r="I1681" s="2" t="inlineStr"/>
       <c r="J1681" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-nolan-azul-c-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/total-look-glaviano-nina</t>
         </is>
       </c>
       <c r="K1681" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-16at1.33.14PM_1.jpg?v=1784820305</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookglavianonina_5EDITARFOTOS.jpg?v=1792793335</t>
         </is>
       </c>
       <c r="L1681" s="2" t="n">
@@ -71586,11 +71586,11 @@
     </row>
     <row r="1682">
       <c r="A1682" s="2" t="n">
-        <v>7643890843715</v>
+        <v>15436722733123</v>
       </c>
       <c r="B1682" s="2" t="inlineStr">
         <is>
-          <t>total look nolan gris c hombre</t>
+          <t>total look glaviano niño</t>
         </is>
       </c>
       <c r="C1682" s="2" t="inlineStr">
@@ -71614,12 +71614,12 @@
       <c r="I1682" s="2" t="inlineStr"/>
       <c r="J1682" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-nolan-gris-c-hombre-1</t>
+          <t>https://tiendasopenmind.com/products/total-look-glaviano-nino</t>
         </is>
       </c>
       <c r="K1682" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-16at1.33.14PM.jpg?v=1784820219</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookglavianonino_5EDITARFOTOS.jpg?v=1792793310</t>
         </is>
       </c>
       <c r="L1682" s="2" t="n">
@@ -71628,11 +71628,11 @@
     </row>
     <row r="1683">
       <c r="A1683" s="2" t="n">
-        <v>7781184929859</v>
+        <v>15436723028035</v>
       </c>
       <c r="B1683" s="2" t="inlineStr">
         <is>
-          <t>total look palermo niño</t>
+          <t>total look jostin niño</t>
         </is>
       </c>
       <c r="C1683" s="2" t="inlineStr">
@@ -71656,12 +71656,12 @@
       <c r="I1683" s="2" t="inlineStr"/>
       <c r="J1683" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-palermo-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-jostin-nino</t>
         </is>
       </c>
       <c r="K1683" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookpalermonino_5EDITARFOTOS.jpg?v=1792794277</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/b0c0a9bb-34b3-40b9-8008-ef2f75dd06ed.jpg?v=1792793498</t>
         </is>
       </c>
       <c r="L1683" s="2" t="n">
@@ -71670,11 +71670,11 @@
     </row>
     <row r="1684">
       <c r="A1684" s="2" t="n">
-        <v>7840603471939</v>
+        <v>7643891138627</v>
       </c>
       <c r="B1684" s="2" t="inlineStr">
         <is>
-          <t>total look snoop hombre</t>
+          <t>total look nolan azul c hombre</t>
         </is>
       </c>
       <c r="C1684" s="2" t="inlineStr">
@@ -71698,12 +71698,12 @@
       <c r="I1684" s="2" t="inlineStr"/>
       <c r="J1684" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-snoop-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-nolan-azul-c-hombre-1</t>
         </is>
       </c>
       <c r="K1684" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/snoop.jpg?v=1789256616</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-16at1.33.14PM_1.jpg?v=1784820305</t>
         </is>
       </c>
       <c r="L1684" s="2" t="n">
@@ -71712,11 +71712,11 @@
     </row>
     <row r="1685">
       <c r="A1685" s="2" t="n">
-        <v>10272920076355</v>
+        <v>7643890843715</v>
       </c>
       <c r="B1685" s="2" t="inlineStr">
         <is>
-          <t>total look snoop niño</t>
+          <t>total look nolan gris c hombre</t>
         </is>
       </c>
       <c r="C1685" s="2" t="inlineStr">
@@ -71740,12 +71740,12 @@
       <c r="I1685" s="2" t="inlineStr"/>
       <c r="J1685" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-snoop-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-nolan-gris-c-hombre-1</t>
         </is>
       </c>
       <c r="K1685" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/snoop_21af7719-01ce-450b-a6b9-8ab450ffaaa1.jpg?v=1790466140</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-16at1.33.14PM.jpg?v=1784820219</t>
         </is>
       </c>
       <c r="L1685" s="2" t="n">
@@ -71754,11 +71754,11 @@
     </row>
     <row r="1686">
       <c r="A1686" s="2" t="n">
-        <v>10272919945283</v>
+        <v>7781184929859</v>
       </c>
       <c r="B1686" s="2" t="inlineStr">
         <is>
-          <t>total look thag niño</t>
+          <t>total look palermo niño</t>
         </is>
       </c>
       <c r="C1686" s="2" t="inlineStr">
@@ -71782,12 +71782,12 @@
       <c r="I1686" s="2" t="inlineStr"/>
       <c r="J1686" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-thag-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-palermo-nino</t>
         </is>
       </c>
       <c r="K1686" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/thag_cc713521-a9c1-4082-bf5e-6670bb32c3c1.jpg?v=1790465979</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookpalermonino_5EDITARFOTOS.jpg?v=1792794277</t>
         </is>
       </c>
       <c r="L1686" s="2" t="n">
@@ -71796,11 +71796,11 @@
     </row>
     <row r="1687">
       <c r="A1687" s="2" t="n">
-        <v>7669786411075</v>
+        <v>7840603471939</v>
       </c>
       <c r="B1687" s="2" t="inlineStr">
         <is>
-          <t>total look trento hombre</t>
+          <t>total look snoop hombre</t>
         </is>
       </c>
       <c r="C1687" s="2" t="inlineStr">
@@ -71824,12 +71824,12 @@
       <c r="I1687" s="2" t="inlineStr"/>
       <c r="J1687" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-trento-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-snoop-hombre</t>
         </is>
       </c>
       <c r="K1687" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/trento.jpg?v=1790462686</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/snoop.jpg?v=1789256616</t>
         </is>
       </c>
       <c r="L1687" s="2" t="n">
@@ -71838,11 +71838,11 @@
     </row>
     <row r="1688">
       <c r="A1688" s="2" t="n">
-        <v>7669786247235</v>
+        <v>10272920076355</v>
       </c>
       <c r="B1688" s="2" t="inlineStr">
         <is>
-          <t>total look trento niño</t>
+          <t>total look snoop niño</t>
         </is>
       </c>
       <c r="C1688" s="2" t="inlineStr">
@@ -71866,12 +71866,12 @@
       <c r="I1688" s="2" t="inlineStr"/>
       <c r="J1688" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-trento-nino</t>
+          <t>https://tiendasopenmind.com/products/total-look-snoop-nino</t>
         </is>
       </c>
       <c r="K1688" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallooktrento_5EDITARFOTOS.jpg?v=1792794486</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/snoop_21af7719-01ce-450b-a6b9-8ab450ffaaa1.jpg?v=1790466140</t>
         </is>
       </c>
       <c r="L1688" s="2" t="n">
@@ -71880,11 +71880,11 @@
     </row>
     <row r="1689">
       <c r="A1689" s="2" t="n">
-        <v>7669785854019</v>
+        <v>10272919945283</v>
       </c>
       <c r="B1689" s="2" t="inlineStr">
         <is>
-          <t>total look trento padre e hijo</t>
+          <t>total look thag niño</t>
         </is>
       </c>
       <c r="C1689" s="2" t="inlineStr">
@@ -71908,12 +71908,12 @@
       <c r="I1689" s="2" t="inlineStr"/>
       <c r="J1689" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-trento-padre-e-hijo</t>
+          <t>https://tiendasopenmind.com/products/total-look-thag-nino</t>
         </is>
       </c>
       <c r="K1689" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallooktrentopadreehijo.jpg?v=1779912981</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/thag_cc713521-a9c1-4082-bf5e-6670bb32c3c1.jpg?v=1790465979</t>
         </is>
       </c>
       <c r="L1689" s="2" t="n">
@@ -71922,11 +71922,11 @@
     </row>
     <row r="1690">
       <c r="A1690" s="2" t="n">
-        <v>7642228260931</v>
+        <v>7669786411075</v>
       </c>
       <c r="B1690" s="2" t="inlineStr">
         <is>
-          <t>total look trust choco hombre</t>
+          <t>total look trento hombre</t>
         </is>
       </c>
       <c r="C1690" s="2" t="inlineStr">
@@ -71950,12 +71950,12 @@
       <c r="I1690" s="2" t="inlineStr"/>
       <c r="J1690" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-trust-choco-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-trento-hombre</t>
         </is>
       </c>
       <c r="K1690" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.38AM.jpg?v=1784821336</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/trento.jpg?v=1790462686</t>
         </is>
       </c>
       <c r="L1690" s="2" t="n">
@@ -71964,11 +71964,11 @@
     </row>
     <row r="1691">
       <c r="A1691" s="2" t="n">
-        <v>7642229047363</v>
+        <v>7669786247235</v>
       </c>
       <c r="B1691" s="2" t="inlineStr">
         <is>
-          <t>total look trust collage hombre</t>
+          <t>total look trento niño</t>
         </is>
       </c>
       <c r="C1691" s="2" t="inlineStr">
@@ -71992,12 +71992,12 @@
       <c r="I1691" s="2" t="inlineStr"/>
       <c r="J1691" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-trust-collage-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-trento-nino</t>
         </is>
       </c>
       <c r="K1691" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.38AM_1.jpg?v=1784821382</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallooktrento_5EDITARFOTOS.jpg?v=1792794486</t>
         </is>
       </c>
       <c r="L1691" s="2" t="n">
@@ -72006,11 +72006,11 @@
     </row>
     <row r="1692">
       <c r="A1692" s="2" t="n">
-        <v>7642227802179</v>
+        <v>7669785854019</v>
       </c>
       <c r="B1692" s="2" t="inlineStr">
         <is>
-          <t>total look trust v militar hombre</t>
+          <t>total look trento padre e hijo</t>
         </is>
       </c>
       <c r="C1692" s="2" t="inlineStr">
@@ -72034,12 +72034,12 @@
       <c r="I1692" s="2" t="inlineStr"/>
       <c r="J1692" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-trust-v-militar-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-trento-padre-e-hijo</t>
         </is>
       </c>
       <c r="K1692" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.39AM.jpg?v=1784821439</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallooktrentopadreehijo.jpg?v=1779912981</t>
         </is>
       </c>
       <c r="L1692" s="2" t="n">
@@ -72048,11 +72048,11 @@
     </row>
     <row r="1693">
       <c r="A1693" s="2" t="n">
-        <v>7778847359043</v>
+        <v>7642228260931</v>
       </c>
       <c r="B1693" s="2" t="inlineStr">
         <is>
-          <t>total look usher hombre</t>
+          <t>total look trust choco hombre</t>
         </is>
       </c>
       <c r="C1693" s="2" t="inlineStr">
@@ -72076,12 +72076,12 @@
       <c r="I1693" s="2" t="inlineStr"/>
       <c r="J1693" s="2" t="inlineStr">
         <is>
-          <t>https://tiendasopenmind.com/products/total-look-usher-hombre</t>
+          <t>https://tiendasopenmind.com/products/total-look-trust-choco-hombre</t>
         </is>
       </c>
       <c r="K1693" s="2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-11at1.04.38PM.jpg?v=1785336992</t>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.38AM.jpg?v=1784821336</t>
         </is>
       </c>
       <c r="L1693" s="2" t="n">
@@ -72090,11 +72090,11 @@
     </row>
     <row r="1694">
       <c r="A1694" s="2" t="n">
-        <v>7778847490115</v>
+        <v>7642229047363</v>
       </c>
       <c r="B1694" s="2" t="inlineStr">
         <is>
-          <t>total look usher niño</t>
+          <t>total look trust collage hombre</t>
         </is>
       </c>
       <c r="C1694" s="2" t="inlineStr">
@@ -72118,20 +72118,146 @@
       <c r="I1694" s="2" t="inlineStr"/>
       <c r="J1694" s="2" t="inlineStr">
         <is>
+          <t>https://tiendasopenmind.com/products/total-look-trust-collage-hombre</t>
+        </is>
+      </c>
+      <c r="K1694" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.38AM_1.jpg?v=1784821382</t>
+        </is>
+      </c>
+      <c r="L1694" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="2" t="n">
+        <v>7642227802179</v>
+      </c>
+      <c r="B1695" s="2" t="inlineStr">
+        <is>
+          <t>total look trust v militar hombre</t>
+        </is>
+      </c>
+      <c r="C1695" s="2" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="D1695" s="2" t="inlineStr"/>
+      <c r="E1695" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1695" s="3" t="n"/>
+      <c r="G1695" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1695" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I1695" s="2" t="inlineStr"/>
+      <c r="J1695" s="2" t="inlineStr">
+        <is>
+          <t>https://tiendasopenmind.com/products/total-look-trust-v-militar-hombre</t>
+        </is>
+      </c>
+      <c r="K1695" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-17at10.33.39AM.jpg?v=1784821439</t>
+        </is>
+      </c>
+      <c r="L1695" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="2" t="n">
+        <v>7778847359043</v>
+      </c>
+      <c r="B1696" s="2" t="inlineStr">
+        <is>
+          <t>total look usher hombre</t>
+        </is>
+      </c>
+      <c r="C1696" s="2" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="D1696" s="2" t="inlineStr"/>
+      <c r="E1696" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1696" s="3" t="n"/>
+      <c r="G1696" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1696" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I1696" s="2" t="inlineStr"/>
+      <c r="J1696" s="2" t="inlineStr">
+        <is>
+          <t>https://tiendasopenmind.com/products/total-look-usher-hombre</t>
+        </is>
+      </c>
+      <c r="K1696" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/WhatsAppImage2026-07-11at1.04.38PM.jpg?v=1785336992</t>
+        </is>
+      </c>
+      <c r="L1696" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="2" t="n">
+        <v>7778847490115</v>
+      </c>
+      <c r="B1697" s="2" t="inlineStr">
+        <is>
+          <t>total look usher niño</t>
+        </is>
+      </c>
+      <c r="C1697" s="2" t="inlineStr">
+        <is>
+          <t>Sin categoría</t>
+        </is>
+      </c>
+      <c r="D1697" s="2" t="inlineStr"/>
+      <c r="E1697" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1697" s="3" t="n"/>
+      <c r="G1697" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1697" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I1697" s="2" t="inlineStr"/>
+      <c r="J1697" s="2" t="inlineStr">
+        <is>
           <t>https://tiendasopenmind.com/products/total-look-usher-nino</t>
         </is>
       </c>
-      <c r="K1694" s="2" t="inlineStr">
+      <c r="K1697" s="2" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0597/2600/4291/files/totallookushernino_5EDITARFOTOS.jpg?v=1792793700</t>
         </is>
       </c>
-      <c r="L1694" s="2" t="n">
+      <c r="L1697" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1694"/>
+  <autoFilter ref="A1:L1697"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -72177,7 +72303,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -72230,7 +72356,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-26 06:40</t>
+          <t>2026-10-26 14:42</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -73398,7 +73398,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 00:34</t>
+          <t>2026-10-27 06:37</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -73398,7 +73398,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 06:37</t>
+          <t>2026-10-27 12:39</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -75036,7 +75036,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-28 00:44</t>
+          <t>2026-10-28 06:43</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -75036,7 +75036,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-28 06:43</t>
+          <t>2026-10-28 12:44</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -75414,7 +75414,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:44</t>
+          <t>2026-10-29 06:46</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -75414,7 +75414,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 06:46</t>
+          <t>2026-10-29 12:46</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -74516,7 +74516,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:45</t>
+          <t>2026-10-30 06:47</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -74516,7 +74516,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 06:47</t>
+          <t>2026-10-30 12:46</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -74452,7 +74452,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-31 00:51</t>
+          <t>2026-10-31 06:44</t>
         </is>
       </c>
     </row>

--- a/OpenMind_Catalogo.xlsx
+++ b/OpenMind_Catalogo.xlsx
@@ -74452,7 +74452,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-31 06:44</t>
+          <t>2026-10-31 12:41</t>
         </is>
       </c>
     </row>
